--- a/utils/monday_sprint_sprint_2024-42.xlsx
+++ b/utils/monday_sprint_sprint_2024-42.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="153">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>27064</t>
+    <t>7060352655</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,7 +87,7 @@
     <t>19/07/2024</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>18/08/2024</t>
   </si>
   <si>
     <t>Feito</t>
@@ -102,13 +102,16 @@
     <t>Julho</t>
   </si>
   <si>
-    <t>26896</t>
+    <t>7061025000</t>
   </si>
   <si>
     <t>Margem de Contribuição nas Ofertas</t>
   </si>
   <si>
-    <t>26829</t>
+    <t>14/08/2024</t>
+  </si>
+  <si>
+    <t>7113184736</t>
   </si>
   <si>
     <t>Segregação custeiro - Fundição - 5.1.2.01.199-Outros materiais diretos</t>
@@ -117,16 +120,19 @@
     <t>29/07/2024</t>
   </si>
   <si>
+    <t>06/08/2024</t>
+  </si>
+  <si>
     <t>Semana 5</t>
   </si>
   <si>
-    <t>26830</t>
+    <t>7113198582</t>
   </si>
   <si>
     <t>Segregação custeiro - Acabamento - Beneficiamento de terceiros</t>
   </si>
   <si>
-    <t>27013</t>
+    <t>7152668146</t>
   </si>
   <si>
     <t>in company</t>
@@ -141,7 +147,7 @@
     <t>Agosto</t>
   </si>
   <si>
-    <t>25636</t>
+    <t>7162031514</t>
   </si>
   <si>
     <t>Bloquear o retorno de tela quando confirmar o regisrtro</t>
@@ -150,13 +156,22 @@
     <t>05/08/2024</t>
   </si>
   <si>
+    <t>13/08/2024</t>
+  </si>
+  <si>
+    <t>7162070675</t>
+  </si>
+  <si>
     <t>Verificar mensagem não existe PDI para sequências que já possuem o desenho</t>
   </si>
   <si>
+    <t>7162092227</t>
+  </si>
+  <si>
     <t>Não permitir cadastrar mais de uma vez o mesmo desenho</t>
   </si>
   <si>
-    <t>24641</t>
+    <t>7178866741</t>
   </si>
   <si>
     <t>Gravar tempo de aciaria e apontamento no cálculo do custeio.</t>
@@ -165,7 +180,7 @@
     <t>07/08/2024</t>
   </si>
   <si>
-    <t>24746</t>
+    <t>6277580526</t>
   </si>
   <si>
     <t>Projeto</t>
@@ -183,118 +198,124 @@
     <t>Março</t>
   </si>
   <si>
-    <t>27121</t>
+    <t>7152653605</t>
   </si>
   <si>
     <t>SIC WEB</t>
   </si>
   <si>
-    <t>27029</t>
+    <t>7060471708</t>
   </si>
   <si>
     <t>Upload de Recibo de Embarque</t>
   </si>
   <si>
-    <t>27269</t>
+    <t>15/08/2024</t>
+  </si>
+  <si>
+    <t>7152027755</t>
   </si>
   <si>
     <t>Melhoria no sistema Controle de PO em Aberto</t>
   </si>
   <si>
-    <t>27252</t>
+    <t>11/08/2024</t>
+  </si>
+  <si>
+    <t>7152058437</t>
   </si>
   <si>
     <t>Relatório de entradas na portaria</t>
   </si>
   <si>
-    <t>27238</t>
+    <t>7152066221</t>
   </si>
   <si>
     <t>Alteração tela manutenção SS</t>
   </si>
   <si>
-    <t>27234</t>
+    <t>7152082110</t>
   </si>
   <si>
     <t>PESO CONJUNTO OTF MESTRE</t>
   </si>
   <si>
-    <t>27233</t>
+    <t>7152244663</t>
   </si>
   <si>
     <t>MELHORIA CÓPIA DOS ANEXOS DO CPP</t>
   </si>
   <si>
-    <t>27232</t>
+    <t>7152270332</t>
   </si>
   <si>
     <t>BOTÃO "SIM" NA ANÁLISE CRÍTICA</t>
   </si>
   <si>
-    <t>27228</t>
+    <t>7152288915</t>
   </si>
   <si>
     <t>Tempo padrão - CPP</t>
   </si>
   <si>
-    <t>27213</t>
+    <t>17/08/2024</t>
+  </si>
+  <si>
+    <t>7152317736</t>
   </si>
   <si>
     <t>Ajuste Tela PCP</t>
   </si>
   <si>
-    <t>27205</t>
+    <t>7152350256</t>
   </si>
   <si>
     <t>Setores Ensaios Mecânicos - Autorização para Movimentação</t>
   </si>
   <si>
-    <t>27204</t>
+    <t>7152497347</t>
   </si>
   <si>
     <t>Melhoria sistemas de corridas</t>
   </si>
   <si>
-    <t>27201</t>
+    <t>7152516522</t>
   </si>
   <si>
     <t>Melhoria Sistema de Embalagens - Analise</t>
   </si>
   <si>
-    <t>27171</t>
+    <t>7152589024</t>
   </si>
   <si>
     <t>Melhoria Sistema de Embalagens II</t>
   </si>
   <si>
-    <t>27167</t>
+    <t>7152595284</t>
   </si>
   <si>
     <t>EMAIL PARA RESPONSAVEIS DO SETOR 613</t>
   </si>
   <si>
-    <t>27279</t>
+    <t>7161557120</t>
   </si>
   <si>
     <t>Ajuste consulta Fluxo</t>
   </si>
   <si>
-    <t>27281</t>
+    <t>7163281460</t>
   </si>
   <si>
     <t>Substituir roteiro</t>
   </si>
   <si>
-    <t>27301</t>
+    <t>7173892965</t>
   </si>
   <si>
     <t>Trava de Refugo - Setores 7235 e 7601 - Radiografia</t>
   </si>
   <si>
-    <t>06/08/2024</t>
-  </si>
-  <si>
-    <t>27278</t>
+    <t>7191932646</t>
   </si>
   <si>
     <t>Atividades complementares CPP bloqueados</t>
@@ -306,7 +327,7 @@
     <t>Semana 2</t>
   </si>
   <si>
-    <t>26510</t>
+    <t>6900458903</t>
   </si>
   <si>
     <t>Planilha Proex - PROEX</t>
@@ -321,7 +342,7 @@
     <t>Junho</t>
   </si>
   <si>
-    <t>25402</t>
+    <t>6891486996</t>
   </si>
   <si>
     <t>Integração da Abertura da CPC e geração da OTF - Parte III (Aplicar na regra de negocio)</t>
@@ -330,13 +351,19 @@
     <t>24/06/2024</t>
   </si>
   <si>
+    <t>19/08/2024</t>
+  </si>
+  <si>
+    <t>7069520123</t>
+  </si>
+  <si>
     <t>Criar documento cobrança evenos para cliente</t>
   </si>
   <si>
     <t>22/07/2024</t>
   </si>
   <si>
-    <t>27069</t>
+    <t>7060295373</t>
   </si>
   <si>
     <t>ATUALIZAÇÃO CALCULO COMISSÃO DA INVOICE</t>
@@ -345,7 +372,7 @@
     <t>Implantação</t>
   </si>
   <si>
-    <t>27284</t>
+    <t>7206310081</t>
   </si>
   <si>
     <t>Excluir Sequencias</t>
@@ -360,7 +387,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2024-42</t>
+    <t>Mar/2024</t>
   </si>
   <si>
     <t>Base</t>
@@ -1005,7 +1032,7 @@
         <v>23</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>25</v>
@@ -1022,7 +1049,7 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>16</v>
@@ -1034,10 +1061,10 @@
         <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>20</v>
@@ -1049,10 +1076,10 @@
         <v>22</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>25</v>
@@ -1061,7 +1088,7 @@
         <v>26</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O4" s="2" t="s">
         <v>28</v>
@@ -1069,46 +1096,46 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="K5" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="L5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N5" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="O5" s="2" t="s">
         <v>28</v>
@@ -1116,7 +1143,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
@@ -1128,10 +1155,10 @@
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>20</v>
@@ -1143,10 +1170,10 @@
         <v>22</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>25</v>
@@ -1155,156 +1182,156 @@
         <v>26</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N7" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="O7" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N8" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="O8" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N9" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="O9" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
@@ -1316,10 +1343,10 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>20</v>
@@ -1331,10 +1358,10 @@
         <v>22</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>25</v>
@@ -1343,33 +1370,33 @@
         <v>26</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>21</v>
@@ -1378,10 +1405,10 @@
         <v>22</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>25</v>
@@ -1393,12 +1420,12 @@
         <v>27</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
@@ -1410,10 +1437,10 @@
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>20</v>
@@ -1425,7 +1452,7 @@
         <v>22</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>24</v>
@@ -1437,15 +1464,15 @@
         <v>26</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
@@ -1457,10 +1484,10 @@
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>20</v>
@@ -1475,7 +1502,7 @@
         <v>23</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>25</v>
@@ -1492,7 +1519,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
@@ -1504,10 +1531,10 @@
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>20</v>
@@ -1519,10 +1546,10 @@
         <v>22</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>25</v>
@@ -1531,15 +1558,15 @@
         <v>26</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
@@ -1551,10 +1578,10 @@
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>20</v>
@@ -1566,10 +1593,10 @@
         <v>22</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>25</v>
@@ -1578,15 +1605,15 @@
         <v>26</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -1598,10 +1625,10 @@
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>20</v>
@@ -1613,10 +1640,10 @@
         <v>22</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>25</v>
@@ -1625,15 +1652,15 @@
         <v>26</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
@@ -1645,10 +1672,10 @@
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>20</v>
@@ -1660,10 +1687,10 @@
         <v>22</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>25</v>
@@ -1672,15 +1699,15 @@
         <v>26</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
@@ -1692,10 +1719,10 @@
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>20</v>
@@ -1707,10 +1734,10 @@
         <v>22</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>25</v>
@@ -1719,15 +1746,15 @@
         <v>26</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
@@ -1739,10 +1766,10 @@
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>20</v>
@@ -1754,10 +1781,10 @@
         <v>22</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>25</v>
@@ -1766,15 +1793,15 @@
         <v>26</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
@@ -1786,10 +1813,10 @@
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>20</v>
@@ -1801,10 +1828,10 @@
         <v>22</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>25</v>
@@ -1813,15 +1840,15 @@
         <v>26</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
@@ -1833,10 +1860,10 @@
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>20</v>
@@ -1848,10 +1875,10 @@
         <v>22</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>25</v>
@@ -1860,15 +1887,15 @@
         <v>26</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
@@ -1880,10 +1907,10 @@
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>20</v>
@@ -1895,10 +1922,10 @@
         <v>22</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>25</v>
@@ -1907,15 +1934,15 @@
         <v>26</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
@@ -1927,10 +1954,10 @@
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>20</v>
@@ -1942,10 +1969,10 @@
         <v>22</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>25</v>
@@ -1954,15 +1981,15 @@
         <v>26</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
@@ -1974,10 +2001,10 @@
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>20</v>
@@ -1989,10 +2016,10 @@
         <v>22</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>25</v>
@@ -2001,15 +2028,15 @@
         <v>26</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
@@ -2021,10 +2048,10 @@
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>20</v>
@@ -2036,10 +2063,10 @@
         <v>22</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>25</v>
@@ -2048,15 +2075,15 @@
         <v>26</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
@@ -2068,10 +2095,10 @@
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>20</v>
@@ -2083,10 +2110,10 @@
         <v>22</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>25</v>
@@ -2095,15 +2122,15 @@
         <v>26</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
@@ -2115,10 +2142,10 @@
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>20</v>
@@ -2130,10 +2157,10 @@
         <v>22</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>25</v>
@@ -2142,15 +2169,15 @@
         <v>26</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
@@ -2162,13 +2189,13 @@
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>21</v>
@@ -2177,10 +2204,10 @@
         <v>22</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>25</v>
@@ -2189,15 +2216,15 @@
         <v>26</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
@@ -2209,13 +2236,13 @@
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>21</v>
@@ -2224,10 +2251,10 @@
         <v>22</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>92</v>
+        <v>35</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>25</v>
@@ -2236,15 +2263,15 @@
         <v>26</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
@@ -2256,10 +2283,10 @@
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>20</v>
@@ -2271,10 +2298,10 @@
         <v>22</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>25</v>
@@ -2283,30 +2310,30 @@
         <v>26</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>20</v>
@@ -2318,10 +2345,10 @@
         <v>22</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>25</v>
@@ -2330,15 +2357,15 @@
         <v>26</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>16</v>
@@ -2350,10 +2377,10 @@
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>20</v>
@@ -2365,10 +2392,10 @@
         <v>22</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>24</v>
+        <v>112</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>25</v>
@@ -2377,30 +2404,30 @@
         <v>26</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>50</v>
+        <v>113</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>20</v>
@@ -2412,10 +2439,10 @@
         <v>22</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>25</v>
@@ -2424,7 +2451,7 @@
         <v>26</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="O33" s="2" t="s">
         <v>28</v>
@@ -2432,7 +2459,7 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>16</v>
@@ -2444,10 +2471,10 @@
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>20</v>
@@ -2462,10 +2489,10 @@
         <v>23</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="M34" s="2" t="s">
         <v>26</v>
@@ -2479,7 +2506,7 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>16</v>
@@ -2491,10 +2518,10 @@
         <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>20</v>
@@ -2506,10 +2533,10 @@
         <v>22</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>25</v>
@@ -2518,10 +2545,10 @@
         <v>26</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -2537,23 +2564,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="B2" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="D2" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="E2" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -2561,16 +2588,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -2581,7 +2608,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>0</v>
+        <v>19.71</v>
       </c>
       <c r="J5" s="4">
         <v>1</v>
@@ -2589,7 +2616,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -2602,7 +2629,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="K23">
         <v>1</v>
@@ -2610,7 +2637,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -2641,12 +2668,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="B2">
         <v>34</v>
@@ -2660,7 +2687,7 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0</v>
+        <v>19.71</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -2670,25 +2697,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -2705,13 +2732,13 @@
         <v>31</v>
       </c>
       <c r="G10" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -2723,21 +2750,21 @@
         <v>33</v>
       </c>
       <c r="P10" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Q10">
-        <v>22</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D11" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E11">
         <v>3</v>
       </c>
       <c r="G11" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="H11">
         <v>3</v>
@@ -2749,16 +2776,16 @@
         <v>34</v>
       </c>
       <c r="M11" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="N11">
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="Q11">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="7:17" x14ac:dyDescent="0.25">
@@ -2769,13 +2796,13 @@
         <v>31</v>
       </c>
       <c r="J12" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -2784,52 +2811,40 @@
         <v>27</v>
       </c>
       <c r="Q12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="7:17" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G13" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="N13">
         <v>0</v>
       </c>
-      <c r="P13" t="s">
-        <v>100</v>
-      </c>
-      <c r="Q13">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="7:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="N14">
         <v>1</v>
       </c>
-      <c r="P14" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q14">
-        <v>2</v>
-      </c>
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -2837,7 +2852,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -2845,7 +2860,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -2853,10 +2868,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -2864,7 +2879,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -2872,142 +2887,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>15</v>
+        <v>109</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>19</v>
+        <v>110</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>35</v>
+        <v>79</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>36</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>37</v>
+        <v>84</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>38</v>
+        <v>85</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>42</v>
+        <v>92</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>43</v>
+        <v>93</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>45</v>
+        <v>95</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>46</v>
+        <v>101</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>47</v>
+        <v>104</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>48</v>
+        <v>105</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>50</v>
+        <v>113</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>52</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
